--- a/research/traditional_assets/database/data/china/china_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/china/china_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.10645</v>
+        <v>0.06985</v>
       </c>
       <c r="E2">
-        <v>0.202</v>
+        <v>0.03323</v>
       </c>
       <c r="F2">
-        <v>0.0545</v>
+        <v>0.0635</v>
       </c>
       <c r="G2">
-        <v>0.1282981175323401</v>
+        <v>0.1331864657004353</v>
       </c>
       <c r="H2">
-        <v>0.1282981175323401</v>
+        <v>0.1331864657004353</v>
       </c>
       <c r="I2">
-        <v>0.1481393432659348</v>
+        <v>0.08658129397092479</v>
       </c>
       <c r="J2">
-        <v>0.1311108356114938</v>
+        <v>0.08558692403797669</v>
       </c>
       <c r="K2">
-        <v>29310.4</v>
+        <v>20343.9</v>
       </c>
       <c r="L2">
-        <v>0.07732912896560312</v>
+        <v>0.05985297349586449</v>
       </c>
       <c r="M2">
-        <v>9895.700000000001</v>
+        <v>12610.6</v>
       </c>
       <c r="N2">
-        <v>0.03699581578695507</v>
+        <v>0.04541808764013298</v>
       </c>
       <c r="O2">
-        <v>0.337617364484961</v>
+        <v>0.6198713127768027</v>
       </c>
       <c r="P2">
-        <v>7395.7</v>
+        <v>11686.7</v>
       </c>
       <c r="Q2">
-        <v>0.02764937849930612</v>
+        <v>0.04209058766624443</v>
       </c>
       <c r="R2">
-        <v>0.2523234073912331</v>
+        <v>0.5744572083032259</v>
       </c>
       <c r="S2">
-        <v>2500</v>
+        <v>923.8999999999996</v>
       </c>
       <c r="T2">
-        <v>0.2526349828713482</v>
+        <v>0.07326376223177325</v>
       </c>
       <c r="U2">
-        <v>112239.5</v>
+        <v>76838</v>
       </c>
       <c r="V2">
-        <v>0.4196157791788295</v>
+        <v>0.2767382216621365</v>
       </c>
       <c r="W2">
-        <v>0.1502653916043996</v>
+        <v>0.07075671918157939</v>
       </c>
       <c r="X2">
-        <v>0.08423026295533748</v>
+        <v>0.1255970106396375</v>
       </c>
       <c r="Y2">
-        <v>0.06603512864906214</v>
+        <v>-0.05484029145805808</v>
       </c>
       <c r="Z2">
-        <v>0.8722913090003434</v>
+        <v>0.7471968404303916</v>
       </c>
       <c r="AA2">
-        <v>0.1225427053234783</v>
+        <v>0.0580911541809073</v>
       </c>
       <c r="AB2">
-        <v>0.06021245636710883</v>
+        <v>0.09235365900206138</v>
       </c>
       <c r="AC2">
-        <v>0.06286320192548547</v>
+        <v>-0.03417102289163883</v>
       </c>
       <c r="AD2">
-        <v>373027.5</v>
+        <v>317981.3</v>
       </c>
       <c r="AE2">
-        <v>12.0145440118688</v>
+        <v>0</v>
       </c>
       <c r="AF2">
-        <v>373039.5145440119</v>
+        <v>317981.3</v>
       </c>
       <c r="AG2">
-        <v>260800.0145440119</v>
+        <v>241143.3</v>
       </c>
       <c r="AH2">
-        <v>0.5824000272178059</v>
+        <v>0.5338506392817641</v>
       </c>
       <c r="AI2">
-        <v>0.5901296881647687</v>
+        <v>0.5613267933150874</v>
       </c>
       <c r="AJ2">
-        <v>0.4936761139588822</v>
+        <v>0.4648104700238551</v>
       </c>
       <c r="AK2">
-        <v>0.5016427592892169</v>
+        <v>0.4924873928710597</v>
       </c>
       <c r="AL2">
-        <v>7134.900000000001</v>
+        <v>6100.6</v>
       </c>
       <c r="AM2">
-        <v>7134.900000000001</v>
+        <v>6100.6</v>
       </c>
       <c r="AN2">
-        <v>6.407875712179442</v>
+        <v>10.03358292549784</v>
       </c>
       <c r="AO2">
-        <v>7.869234327040323</v>
+        <v>4.823918958790938</v>
       </c>
       <c r="AP2">
-        <v>4.480029163889041</v>
+        <v>7.609036435407377</v>
       </c>
       <c r="AQ2">
-        <v>7.869234327040323</v>
+        <v>4.823918958790938</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>China Life Insurance Company Limited (SEHK:2628)</t>
+          <t>Sunshine Insurance Group Company Limited (SEHK:6963)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,125 +724,101 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.09390000000000001</v>
-      </c>
-      <c r="E3">
-        <v>0.291</v>
-      </c>
-      <c r="F3">
-        <v>0.101</v>
-      </c>
       <c r="G3">
-        <v>0.08627978463490905</v>
+        <v>0.06735791975043705</v>
       </c>
       <c r="H3">
-        <v>0.08627978463490905</v>
+        <v>0.06735791975043705</v>
       </c>
       <c r="I3">
-        <v>0.08787640445168915</v>
+        <v>0.05347702743726904</v>
       </c>
       <c r="J3">
-        <v>0.08787640445168915</v>
+        <v>0.05347702743726904</v>
       </c>
       <c r="K3">
-        <v>8021.2</v>
+        <v>871.4</v>
       </c>
       <c r="L3">
-        <v>0.06095576808356226</v>
+        <v>0.04561014163534916</v>
       </c>
       <c r="M3">
-        <v>5453.8</v>
+        <v>383.3</v>
       </c>
       <c r="N3">
-        <v>0.04914998233635898</v>
+        <v>0.04741816562337631</v>
       </c>
       <c r="O3">
-        <v>0.6799232035106967</v>
+        <v>0.4398668808813404</v>
       </c>
       <c r="P3">
-        <v>4047.9</v>
+        <v>383.3</v>
       </c>
       <c r="Q3">
-        <v>0.03647992473126032</v>
+        <v>0.04741816562337631</v>
       </c>
       <c r="R3">
-        <v>0.5046501770308682</v>
+        <v>0.4398668808813404</v>
       </c>
       <c r="S3">
-        <v>1405.9</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.257783563753713</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>8974.799999999999</v>
+        <v>1183.7</v>
       </c>
       <c r="V3">
-        <v>0.08088145173500212</v>
-      </c>
-      <c r="W3">
-        <v>0.1304673839672742</v>
+        <v>0.1464359056832521</v>
       </c>
       <c r="X3">
-        <v>0.07391980637029819</v>
-      </c>
-      <c r="Y3">
-        <v>0.05654757759697598</v>
-      </c>
-      <c r="Z3">
-        <v>1.818668682641517</v>
-      </c>
-      <c r="AA3">
-        <v>0.1598180647194266</v>
+        <v>0.1255970106396375</v>
       </c>
       <c r="AB3">
-        <v>0.06109588767771088</v>
-      </c>
-      <c r="AC3">
-        <v>0.09872217704171576</v>
+        <v>0.09500082365674264</v>
       </c>
       <c r="AD3">
-        <v>37895.8</v>
+        <v>5566.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>37895.8</v>
+        <v>5566.6</v>
       </c>
       <c r="AG3">
-        <v>28921</v>
+        <v>4382.900000000001</v>
       </c>
       <c r="AH3">
-        <v>0.2545765030075602</v>
+        <v>0.4078095238095238</v>
       </c>
       <c r="AI3">
-        <v>0.3379630785695176</v>
+        <v>0.4009998703338184</v>
       </c>
       <c r="AJ3">
-        <v>0.2067507652802263</v>
+        <v>0.3515798593006747</v>
       </c>
       <c r="AK3">
-        <v>0.2803639564462093</v>
+        <v>0.3451618746111623</v>
       </c>
       <c r="AL3">
-        <v>2501.9</v>
+        <v>144</v>
       </c>
       <c r="AM3">
-        <v>2501.9</v>
+        <v>144</v>
       </c>
       <c r="AN3">
-        <v>3.129401466605008</v>
+        <v>4.666051969823974</v>
       </c>
       <c r="AO3">
-        <v>4.621967304848315</v>
+        <v>7.095138888888889</v>
       </c>
       <c r="AP3">
-        <v>2.388270463103654</v>
+        <v>3.67384744341995</v>
       </c>
       <c r="AQ3">
-        <v>4.621967304848315</v>
+        <v>7.095138888888889</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New China Life Insurance Company Ltd. (SHSE:601336)</t>
+          <t>Ping An Insurance (Group) Company of China, Ltd. (SEHK:2318)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,124 +838,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0907</v>
+        <v>0.0667</v>
       </c>
       <c r="E4">
-        <v>0.261</v>
+        <v>0.0596</v>
       </c>
       <c r="F4">
-        <v>0.0545</v>
+        <v>0.08960000000000001</v>
       </c>
       <c r="G4">
-        <v>0.08084851206125453</v>
+        <v>0.1700297441526151</v>
       </c>
       <c r="H4">
-        <v>0.08084851206125453</v>
+        <v>0.1700297441526151</v>
       </c>
       <c r="I4">
-        <v>0.07959305451344374</v>
+        <v>0.1215900777910895</v>
       </c>
       <c r="J4">
-        <v>0.0730136270893756</v>
+        <v>0.114607881524718</v>
       </c>
       <c r="K4">
-        <v>2349.8</v>
+        <v>13556.2</v>
       </c>
       <c r="L4">
-        <v>0.069413509314018</v>
+        <v>0.07693525695122719</v>
       </c>
       <c r="M4">
-        <v>726.8</v>
+        <v>7820.299999999999</v>
       </c>
       <c r="N4">
-        <v>0.04680396172224154</v>
+        <v>0.05977803478458947</v>
       </c>
       <c r="O4">
-        <v>0.3093029193973955</v>
+        <v>0.5768799516088579</v>
       </c>
       <c r="P4">
-        <v>726.8</v>
+        <v>6896.4</v>
       </c>
       <c r="Q4">
-        <v>0.04680396172224154</v>
+        <v>0.05271578316540834</v>
       </c>
       <c r="R4">
-        <v>0.3093029193973955</v>
+        <v>0.5087266343075493</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>923.8999999999996</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>0.1181412477782182</v>
       </c>
       <c r="U4">
-        <v>2089.7</v>
+        <v>53556.9</v>
       </c>
       <c r="V4">
-        <v>0.1345710495472869</v>
+        <v>0.409386625980433</v>
       </c>
       <c r="W4">
-        <v>0.1700633992415251</v>
+        <v>0.1105452730687277</v>
       </c>
       <c r="X4">
-        <v>0.07250288040266184</v>
+        <v>0.1887067213433059</v>
       </c>
       <c r="Y4">
-        <v>0.09756051883886321</v>
+        <v>-0.07816144827457819</v>
       </c>
       <c r="Z4">
-        <v>1.921717114375894</v>
+        <v>0.5298174082342948</v>
       </c>
       <c r="AA4">
-        <v>0.1403115367603125</v>
+        <v>0.06072125075264922</v>
       </c>
       <c r="AB4">
-        <v>0.06081336715339521</v>
+        <v>0.09235365900206138</v>
       </c>
       <c r="AC4">
-        <v>0.07949816960691726</v>
+        <v>-0.03163240824941217</v>
       </c>
       <c r="AD4">
-        <v>4676.8</v>
+        <v>282421.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>4676.8</v>
+        <v>282421.5</v>
       </c>
       <c r="AG4">
-        <v>2587.1</v>
+        <v>228864.6</v>
       </c>
       <c r="AH4">
-        <v>0.2314628762608016</v>
+        <v>0.6834258614406314</v>
       </c>
       <c r="AI4">
-        <v>0.2233972935146573</v>
+        <v>0.6437934510400894</v>
       </c>
       <c r="AJ4">
-        <v>0.1428098279393013</v>
+        <v>0.6362883941561397</v>
       </c>
       <c r="AK4">
-        <v>0.1372816420096364</v>
+        <v>0.5942582502112942</v>
       </c>
       <c r="AL4">
-        <v>203.9</v>
+        <v>3332.9</v>
       </c>
       <c r="AM4">
-        <v>203.9</v>
+        <v>3332.9</v>
       </c>
       <c r="AN4">
-        <v>1.656559931992066</v>
+        <v>12.36402360543205</v>
       </c>
       <c r="AO4">
-        <v>13.21432074546346</v>
+        <v>6.428185664136338</v>
       </c>
       <c r="AP4">
-        <v>0.91637149334089</v>
+        <v>10.01937641733283</v>
       </c>
       <c r="AQ4">
-        <v>13.21432074546346</v>
+        <v>6.428185664136338</v>
       </c>
     </row>
     <row r="5">
@@ -990,7 +966,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ping An Insurance (Group) Company of China, Ltd. (SEHK:2318)</t>
+          <t>New China Life Insurance Company Ltd. (SHSE:601336)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -999,124 +975,124 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.119</v>
+        <v>0.077</v>
       </c>
       <c r="E5">
-        <v>0.143</v>
+        <v>0.095</v>
       </c>
       <c r="F5">
-        <v>0.0475</v>
+        <v>0.0374</v>
       </c>
       <c r="G5">
-        <v>0.1659266277355484</v>
+        <v>0.09323890488722324</v>
       </c>
       <c r="H5">
-        <v>0.1659266277355484</v>
+        <v>0.09323890488722324</v>
       </c>
       <c r="I5">
-        <v>0.2019738878530758</v>
+        <v>0.03770478250685479</v>
       </c>
       <c r="J5">
-        <v>0.1747978780673702</v>
+        <v>0.03770478250685479</v>
       </c>
       <c r="K5">
-        <v>18884</v>
+        <v>1150.2</v>
       </c>
       <c r="L5">
-        <v>0.09119018058881505</v>
+        <v>0.03961998980393238</v>
       </c>
       <c r="M5">
-        <v>3681.9</v>
+        <v>708.9</v>
       </c>
       <c r="N5">
-        <v>0.02660019087347372</v>
+        <v>0.06096438799115934</v>
       </c>
       <c r="O5">
-        <v>0.1949745816564287</v>
+        <v>0.6163275952008346</v>
       </c>
       <c r="P5">
-        <v>2587.8</v>
+        <v>708.9</v>
       </c>
       <c r="Q5">
-        <v>0.01869577499181816</v>
+        <v>0.06096438799115934</v>
       </c>
       <c r="R5">
-        <v>0.1370366447786486</v>
+        <v>0.6163275952008346</v>
       </c>
       <c r="S5">
-        <v>1094.1</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.2971563594883077</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>97772</v>
+        <v>1612.4</v>
       </c>
       <c r="V5">
-        <v>0.7063618952392168</v>
+        <v>0.1386640981759703</v>
       </c>
       <c r="W5">
-        <v>0.1807003526163945</v>
+        <v>0.07075671918157939</v>
       </c>
       <c r="X5">
-        <v>0.1451663186336812</v>
+        <v>0.1179577415273157</v>
       </c>
       <c r="Y5">
-        <v>0.03553403398271335</v>
+        <v>-0.04720102234573634</v>
       </c>
       <c r="Z5">
-        <v>0.5994001474449391</v>
+        <v>1.540683974780818</v>
       </c>
       <c r="AA5">
-        <v>0.1047738738866442</v>
+        <v>0.0580911541809073</v>
       </c>
       <c r="AB5">
-        <v>0.05854563964259045</v>
+        <v>0.09226217707254612</v>
       </c>
       <c r="AC5">
-        <v>0.0462282342440537</v>
+        <v>-0.03417102289163883</v>
       </c>
       <c r="AD5">
-        <v>328076.2</v>
+        <v>5938.3</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>328076.2</v>
+        <v>5938.3</v>
       </c>
       <c r="AG5">
-        <v>230304.2</v>
+        <v>4325.9</v>
       </c>
       <c r="AH5">
-        <v>0.7032829037980246</v>
+        <v>0.3380487749339648</v>
       </c>
       <c r="AI5">
-        <v>0.6682991378091643</v>
+        <v>0.2968437574982005</v>
       </c>
       <c r="AJ5">
-        <v>0.6246037310103453</v>
+        <v>0.2711483013664285</v>
       </c>
       <c r="AK5">
-        <v>0.5858067936069626</v>
+        <v>0.235200408864531</v>
       </c>
       <c r="AL5">
-        <v>4429.1</v>
+        <v>117.1</v>
       </c>
       <c r="AM5">
-        <v>4429.1</v>
+        <v>117.1</v>
       </c>
       <c r="AN5">
-        <v>7.593600636973634</v>
+        <v>4.802507076425394</v>
       </c>
       <c r="AO5">
-        <v>9.443340633537288</v>
+        <v>9.347566182749786</v>
       </c>
       <c r="AP5">
-        <v>5.330585150089227</v>
+        <v>3.498503841488071</v>
       </c>
       <c r="AQ5">
-        <v>9.443340633537288</v>
+        <v>9.347566182749786</v>
       </c>
     </row>
     <row r="6">
@@ -1127,124 +1103,258 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>China Life Insurance Company Limited (SEHK:2628)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.073</v>
+      </c>
+      <c r="E6">
+        <v>0.006860000000000001</v>
+      </c>
+      <c r="G6">
+        <v>0.1038361972732758</v>
+      </c>
+      <c r="H6">
+        <v>0.1038361972732758</v>
+      </c>
+      <c r="I6">
+        <v>0.05368019204050416</v>
+      </c>
+      <c r="J6">
+        <v>0.05368019204050416</v>
+      </c>
+      <c r="K6">
+        <v>4716.1</v>
+      </c>
+      <c r="L6">
+        <v>0.04350894608363209</v>
+      </c>
+      <c r="M6">
+        <v>3607.1</v>
+      </c>
+      <c r="N6">
+        <v>0.02888950291730238</v>
+      </c>
+      <c r="O6">
+        <v>0.7648480736201522</v>
+      </c>
+      <c r="P6">
+        <v>3607.1</v>
+      </c>
+      <c r="Q6">
+        <v>0.02888950291730238</v>
+      </c>
+      <c r="R6">
+        <v>0.7648480736201522</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>17037.9</v>
+      </c>
+      <c r="V6">
+        <v>0.1364576700825334</v>
+      </c>
+      <c r="W6">
+        <v>0.06455052381173984</v>
+      </c>
+      <c r="X6">
+        <v>0.1030049121360875</v>
+      </c>
+      <c r="Y6">
+        <v>-0.03845438832434762</v>
+      </c>
+      <c r="Z6">
+        <v>1.062876048228308</v>
+      </c>
+      <c r="AA6">
+        <v>0.05705539038414773</v>
+      </c>
+      <c r="AB6">
+        <v>0.09487461358960687</v>
+      </c>
+      <c r="AC6">
+        <v>-0.03781922320545914</v>
+      </c>
+      <c r="AD6">
+        <v>20271</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>20271</v>
+      </c>
+      <c r="AG6">
+        <v>3233.099999999999</v>
+      </c>
+      <c r="AH6">
+        <v>0.1396752555476316</v>
+      </c>
+      <c r="AI6">
+        <v>0.2378479983385488</v>
+      </c>
+      <c r="AJ6">
+        <v>0.02524053099500669</v>
+      </c>
+      <c r="AK6">
+        <v>0.04741394481205123</v>
+      </c>
+      <c r="AL6">
+        <v>2506.6</v>
+      </c>
+      <c r="AM6">
+        <v>2506.6</v>
+      </c>
+      <c r="AN6">
+        <v>3.199488612150196</v>
+      </c>
+      <c r="AO6">
+        <v>2.321311737014283</v>
+      </c>
+      <c r="AP6">
+        <v>0.5102987830863202</v>
+      </c>
+      <c r="AQ6">
+        <v>2.321311737014283</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>Hubei Biocause Pharmaceutical Co., Ltd. (SZSE:000627)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Insurance (Life)</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.348</v>
-      </c>
-      <c r="E6">
-        <v>-0.208</v>
-      </c>
-      <c r="G6">
-        <v>0.02738168408113091</v>
-      </c>
-      <c r="H6">
-        <v>0.02738168408113091</v>
-      </c>
-      <c r="I6">
-        <v>0.01018855119816015</v>
-      </c>
-      <c r="J6">
-        <v>0.00771699612264207</v>
-      </c>
-      <c r="K6">
-        <v>55.4</v>
-      </c>
-      <c r="L6">
-        <v>0.008512599877074371</v>
-      </c>
-      <c r="M6">
-        <v>33.2</v>
-      </c>
-      <c r="N6">
-        <v>0.01289670978518432</v>
-      </c>
-      <c r="O6">
-        <v>0.5992779783393503</v>
-      </c>
-      <c r="P6">
-        <v>33.2</v>
-      </c>
-      <c r="Q6">
-        <v>0.01289670978518432</v>
-      </c>
-      <c r="R6">
-        <v>0.5992779783393503</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>3403</v>
-      </c>
-      <c r="V6">
-        <v>1.321912752981393</v>
-      </c>
-      <c r="W6">
-        <v>0.0180892052504408</v>
-      </c>
-      <c r="X6">
-        <v>0.09454071954037675</v>
-      </c>
-      <c r="Y6">
-        <v>-0.07645151428993595</v>
-      </c>
-      <c r="Z6">
-        <v>-7.008509510925595</v>
-      </c>
-      <c r="AA6">
-        <v>-0.05408464072131289</v>
-      </c>
-      <c r="AB6">
-        <v>0.05961154558082246</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1136961863021353</v>
-      </c>
-      <c r="AD6">
-        <v>2378.7</v>
-      </c>
-      <c r="AE6">
-        <v>12.0145440118688</v>
-      </c>
-      <c r="AF6">
-        <v>2390.714544011869</v>
-      </c>
-      <c r="AG6">
-        <v>-1012.285455988131</v>
-      </c>
-      <c r="AH6">
-        <v>0.4815120928286558</v>
-      </c>
-      <c r="AI6">
-        <v>0.2931839986191718</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.648064040036518</v>
-      </c>
-      <c r="AK6">
-        <v>-0.2130537657760261</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>30.96862387709933</v>
-      </c>
-      <c r="AP6">
-        <v>-13.17908418159265</v>
+      <c r="D7">
+        <v>-0.0144</v>
+      </c>
+      <c r="E7">
+        <v>-0.275</v>
+      </c>
+      <c r="G7">
+        <v>0.008541282867191425</v>
+      </c>
+      <c r="H7">
+        <v>0.008541282867191425</v>
+      </c>
+      <c r="I7">
+        <v>0.009685703120638644</v>
+      </c>
+      <c r="J7">
+        <v>0.009685703120638644</v>
+      </c>
+      <c r="K7">
+        <v>50</v>
+      </c>
+      <c r="L7">
+        <v>0.006978172277117178</v>
+      </c>
+      <c r="M7">
+        <v>91</v>
+      </c>
+      <c r="N7">
+        <v>0.04020144901926136</v>
+      </c>
+      <c r="O7">
+        <v>1.82</v>
+      </c>
+      <c r="P7">
+        <v>91</v>
+      </c>
+      <c r="Q7">
+        <v>0.04020144901926136</v>
+      </c>
+      <c r="R7">
+        <v>1.82</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>3447.1</v>
+      </c>
+      <c r="V7">
+        <v>1.522839724332921</v>
+      </c>
+      <c r="W7">
+        <v>0.01439511717625381</v>
+      </c>
+      <c r="X7">
+        <v>0.1677933004424598</v>
+      </c>
+      <c r="Y7">
+        <v>-0.153398183266206</v>
+      </c>
+      <c r="Z7">
+        <v>4.775208263912031</v>
+      </c>
+      <c r="AA7">
+        <v>0.0462512495834722</v>
+      </c>
+      <c r="AB7">
+        <v>0.08905128301116036</v>
+      </c>
+      <c r="AC7">
+        <v>-0.04280003342768816</v>
+      </c>
+      <c r="AD7">
+        <v>3783.9</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>3783.9</v>
+      </c>
+      <c r="AG7">
+        <v>336.8000000000002</v>
+      </c>
+      <c r="AH7">
+        <v>0.6256965688300951</v>
+      </c>
+      <c r="AI7">
+        <v>0.4356872272565027</v>
+      </c>
+      <c r="AJ7">
+        <v>0.1295185356099062</v>
+      </c>
+      <c r="AK7">
+        <v>0.0643018061017985</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>44.88612099644129</v>
+      </c>
+      <c r="AP7">
+        <v>3.995255041518389</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/china/china_insurance_life.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06985</v>
+        <v>0.06455</v>
       </c>
       <c r="E2">
-        <v>0.03323</v>
+        <v>-0.0512</v>
       </c>
       <c r="F2">
-        <v>0.0635</v>
+        <v>0.174</v>
       </c>
       <c r="G2">
-        <v>0.1331864657004353</v>
+        <v>0.08141788240995586</v>
       </c>
       <c r="H2">
-        <v>0.1331864657004353</v>
+        <v>0.08141788240995586</v>
       </c>
       <c r="I2">
-        <v>0.08658129397092479</v>
+        <v>0.06127046346528753</v>
       </c>
       <c r="J2">
-        <v>0.08558692403797669</v>
+        <v>0.0594903861454784</v>
       </c>
       <c r="K2">
-        <v>20343.9</v>
+        <v>14922</v>
       </c>
       <c r="L2">
-        <v>0.05985297349586449</v>
+        <v>0.04565385796822281</v>
       </c>
       <c r="M2">
-        <v>12610.6</v>
+        <v>11574.8375</v>
       </c>
       <c r="N2">
-        <v>0.04541808764013298</v>
+        <v>0.05598890122355001</v>
       </c>
       <c r="O2">
-        <v>0.6198713127768027</v>
+        <v>0.7756894183085377</v>
       </c>
       <c r="P2">
-        <v>11686.7</v>
+        <v>10964.8375</v>
       </c>
       <c r="Q2">
-        <v>0.04209058766624443</v>
+        <v>0.05303825679797034</v>
       </c>
       <c r="R2">
-        <v>0.5744572083032259</v>
+        <v>0.7348101796005897</v>
       </c>
       <c r="S2">
-        <v>923.8999999999996</v>
+        <v>610</v>
       </c>
       <c r="T2">
-        <v>0.07326376223177325</v>
+        <v>0.05270052387344531</v>
       </c>
       <c r="U2">
-        <v>76838</v>
+        <v>90759.3</v>
       </c>
       <c r="V2">
-        <v>0.2767382216621365</v>
+        <v>0.4390138075647751</v>
       </c>
       <c r="W2">
-        <v>0.07075671918157939</v>
+        <v>0.07866295026948619</v>
       </c>
       <c r="X2">
-        <v>0.1255970106396375</v>
+        <v>0.1217792936685995</v>
       </c>
       <c r="Y2">
-        <v>-0.05484029145805808</v>
+        <v>-0.04311634339911333</v>
       </c>
       <c r="Z2">
-        <v>0.7471968404303916</v>
+        <v>0.7310530022753507</v>
       </c>
       <c r="AA2">
-        <v>0.0580911541809073</v>
+        <v>0.0421335395936115</v>
       </c>
       <c r="AB2">
-        <v>0.09235365900206138</v>
+        <v>0.07945396487885244</v>
       </c>
       <c r="AC2">
-        <v>-0.03417102289163883</v>
+        <v>-0.03866114248696154</v>
       </c>
       <c r="AD2">
-        <v>317981.3</v>
+        <v>327947.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>317981.3</v>
+        <v>327947.2</v>
       </c>
       <c r="AG2">
-        <v>241143.3</v>
+        <v>237187.9</v>
       </c>
       <c r="AH2">
-        <v>0.5338506392817641</v>
+        <v>0.6133503353490498</v>
       </c>
       <c r="AI2">
-        <v>0.5613267933150874</v>
+        <v>0.5583723277880418</v>
       </c>
       <c r="AJ2">
-        <v>0.4648104700238551</v>
+        <v>0.5343003642077985</v>
       </c>
       <c r="AK2">
-        <v>0.4924873928710597</v>
+        <v>0.477654612320815</v>
       </c>
       <c r="AL2">
-        <v>6100.6</v>
+        <v>3255</v>
       </c>
       <c r="AM2">
-        <v>6100.6</v>
+        <v>2281.5</v>
       </c>
       <c r="AN2">
-        <v>10.03358292549784</v>
+        <v>14.35462507824093</v>
       </c>
       <c r="AO2">
-        <v>4.823918958790938</v>
+        <v>6.152473118279571</v>
       </c>
       <c r="AP2">
-        <v>7.609036435407377</v>
+        <v>10.38198642219022</v>
       </c>
       <c r="AQ2">
-        <v>4.823918958790938</v>
+        <v>8.777690116151655</v>
       </c>
     </row>
     <row r="3">
@@ -725,40 +725,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.06735791975043705</v>
+        <v>0.05997017291945025</v>
       </c>
       <c r="H3">
-        <v>0.06735791975043705</v>
+        <v>0.05997017291945025</v>
       </c>
       <c r="I3">
-        <v>0.05347702743726904</v>
+        <v>0.04946970998985436</v>
       </c>
       <c r="J3">
-        <v>0.05347702743726904</v>
+        <v>0.04228354688694549</v>
       </c>
       <c r="K3">
-        <v>871.4</v>
+        <v>705.8</v>
       </c>
       <c r="L3">
-        <v>0.04561014163534916</v>
+        <v>0.03913002500374224</v>
       </c>
       <c r="M3">
-        <v>383.3</v>
+        <v>287.5375</v>
       </c>
       <c r="N3">
-        <v>0.04741816562337631</v>
+        <v>0.04489546575898573</v>
       </c>
       <c r="O3">
-        <v>0.4398668808813404</v>
+        <v>0.4073923207707567</v>
       </c>
       <c r="P3">
-        <v>383.3</v>
+        <v>287.5375</v>
       </c>
       <c r="Q3">
-        <v>0.04741816562337631</v>
+        <v>0.04489546575898573</v>
       </c>
       <c r="R3">
-        <v>0.4398668808813404</v>
+        <v>0.4073923207707567</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,58 +767,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1183.7</v>
+        <v>1691.3</v>
       </c>
       <c r="V3">
-        <v>0.1464359056832521</v>
+        <v>0.2640758205040127</v>
+      </c>
+      <c r="W3">
+        <v>0.08675771022580604</v>
       </c>
       <c r="X3">
-        <v>0.1255970106396375</v>
+        <v>0.1114473969901334</v>
+      </c>
+      <c r="Y3">
+        <v>-0.02468968676432735</v>
+      </c>
+      <c r="Z3">
+        <v>1.440886069882251</v>
+      </c>
+      <c r="AA3">
+        <v>0.06092577369461279</v>
       </c>
       <c r="AB3">
-        <v>0.09500082365674264</v>
+        <v>0.07990169400143154</v>
+      </c>
+      <c r="AC3">
+        <v>-0.01897592030681875</v>
       </c>
       <c r="AD3">
-        <v>5566.6</v>
+        <v>5612.4</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5566.6</v>
+        <v>5612.4</v>
       </c>
       <c r="AG3">
-        <v>4382.900000000001</v>
+        <v>3921.099999999999</v>
       </c>
       <c r="AH3">
-        <v>0.4078095238095238</v>
+        <v>0.4670383623200466</v>
       </c>
       <c r="AI3">
-        <v>0.4009998703338184</v>
+        <v>0.3793571935516577</v>
       </c>
       <c r="AJ3">
-        <v>0.3515798593006747</v>
+        <v>0.3797418092720105</v>
       </c>
       <c r="AK3">
-        <v>0.3451618746111623</v>
+        <v>0.2992475120581232</v>
       </c>
       <c r="AL3">
-        <v>144</v>
+        <v>22.8</v>
       </c>
       <c r="AM3">
-        <v>144</v>
+        <v>22.8</v>
       </c>
       <c r="AN3">
-        <v>4.666051969823974</v>
+        <v>5.386697379786927</v>
       </c>
       <c r="AO3">
-        <v>7.095138888888889</v>
+        <v>39.1359649122807</v>
       </c>
       <c r="AP3">
-        <v>3.67384744341995</v>
+        <v>3.76341299548901</v>
       </c>
       <c r="AQ3">
-        <v>7.095138888888889</v>
+        <v>39.1359649122807</v>
       </c>
     </row>
     <row r="4">
@@ -838,124 +853,124 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0667</v>
+        <v>0.0341</v>
       </c>
       <c r="E4">
-        <v>0.0596</v>
+        <v>-0.0512</v>
       </c>
       <c r="F4">
-        <v>0.08960000000000001</v>
+        <v>0.172</v>
       </c>
       <c r="G4">
-        <v>0.1700297441526151</v>
+        <v>0.1190757329349194</v>
       </c>
       <c r="H4">
-        <v>0.1700297441526151</v>
+        <v>0.1190757329349194</v>
       </c>
       <c r="I4">
-        <v>0.1215900777910895</v>
+        <v>0.1021321689677933</v>
       </c>
       <c r="J4">
-        <v>0.114607881524718</v>
+        <v>0.1021321689677933</v>
       </c>
       <c r="K4">
-        <v>13556.2</v>
+        <v>10767.8</v>
       </c>
       <c r="L4">
-        <v>0.07693525695122719</v>
+        <v>0.0632873970047249</v>
       </c>
       <c r="M4">
-        <v>7820.299999999999</v>
+        <v>7567.5</v>
       </c>
       <c r="N4">
-        <v>0.05977803478458947</v>
+        <v>0.08026052454906153</v>
       </c>
       <c r="O4">
-        <v>0.5768799516088579</v>
+        <v>0.7027897992161817</v>
       </c>
       <c r="P4">
-        <v>6896.4</v>
+        <v>6957.5</v>
       </c>
       <c r="Q4">
-        <v>0.05271578316540834</v>
+        <v>0.07379089521639849</v>
       </c>
       <c r="R4">
-        <v>0.5087266343075493</v>
+        <v>0.6461394156652241</v>
       </c>
       <c r="S4">
-        <v>923.8999999999996</v>
+        <v>610</v>
       </c>
       <c r="T4">
-        <v>0.1181412477782182</v>
+        <v>0.08060786257020151</v>
       </c>
       <c r="U4">
-        <v>53556.9</v>
+        <v>61486.6</v>
       </c>
       <c r="V4">
-        <v>0.409386625980433</v>
+        <v>0.6521237884028183</v>
       </c>
       <c r="W4">
-        <v>0.1105452730687277</v>
+        <v>0.09132746185006005</v>
       </c>
       <c r="X4">
-        <v>0.1887067213433059</v>
+        <v>0.1794569480110285</v>
       </c>
       <c r="Y4">
-        <v>-0.07816144827457819</v>
+        <v>-0.08812948616096841</v>
       </c>
       <c r="Z4">
-        <v>0.5298174082342948</v>
+        <v>0.49064907410665</v>
       </c>
       <c r="AA4">
-        <v>0.06072125075264922</v>
+        <v>0.0501110541405517</v>
       </c>
       <c r="AB4">
-        <v>0.09235365900206138</v>
+        <v>0.07826515423242911</v>
       </c>
       <c r="AC4">
-        <v>-0.03163240824941217</v>
+        <v>-0.02815410009187741</v>
       </c>
       <c r="AD4">
-        <v>282421.5</v>
+        <v>277663.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>282421.5</v>
+        <v>277663.4</v>
       </c>
       <c r="AG4">
-        <v>228864.6</v>
+        <v>216176.8</v>
       </c>
       <c r="AH4">
-        <v>0.6834258614406314</v>
+        <v>0.7465071255525942</v>
       </c>
       <c r="AI4">
-        <v>0.6437934510400894</v>
+        <v>0.6218369922861445</v>
       </c>
       <c r="AJ4">
-        <v>0.6362883941561397</v>
+        <v>0.6963034301938876</v>
       </c>
       <c r="AK4">
-        <v>0.5942582502112942</v>
+        <v>0.5614477244382713</v>
       </c>
       <c r="AL4">
-        <v>3332.9</v>
+        <v>3232.2</v>
       </c>
       <c r="AM4">
-        <v>3332.9</v>
+        <v>3232.2</v>
       </c>
       <c r="AN4">
-        <v>12.36402360543205</v>
+        <v>14.3567266278186</v>
       </c>
       <c r="AO4">
-        <v>6.428185664136338</v>
+        <v>5.376183404492297</v>
       </c>
       <c r="AP4">
-        <v>10.01937641733283</v>
+        <v>11.17753085526078</v>
       </c>
       <c r="AQ4">
-        <v>6.428185664136338</v>
+        <v>5.376183404492297</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New China Life Insurance Company Ltd. (SHSE:601336)</t>
+          <t>China Life Insurance Company Limited (SEHK:2628)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,49 +990,49 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.077</v>
+        <v>0.07719999999999999</v>
       </c>
       <c r="E5">
-        <v>0.095</v>
+        <v>-0.0736</v>
       </c>
       <c r="F5">
-        <v>0.0374</v>
+        <v>0.207</v>
       </c>
       <c r="G5">
-        <v>0.09323890488722324</v>
+        <v>0.03869837759870871</v>
       </c>
       <c r="H5">
-        <v>0.09323890488722324</v>
+        <v>0.03869837759870871</v>
       </c>
       <c r="I5">
-        <v>0.03770478250685479</v>
+        <v>0.02691791452701188</v>
       </c>
       <c r="J5">
-        <v>0.03770478250685479</v>
+        <v>0.02691791452701188</v>
       </c>
       <c r="K5">
-        <v>1150.2</v>
+        <v>2366.3</v>
       </c>
       <c r="L5">
-        <v>0.03961998980393238</v>
+        <v>0.02257357661880009</v>
       </c>
       <c r="M5">
-        <v>708.9</v>
+        <v>3028.3</v>
       </c>
       <c r="N5">
-        <v>0.06096438799115934</v>
+        <v>0.03259941675646407</v>
       </c>
       <c r="O5">
-        <v>0.6163275952008346</v>
+        <v>1.279761653213878</v>
       </c>
       <c r="P5">
-        <v>708.9</v>
+        <v>3028.3</v>
       </c>
       <c r="Q5">
-        <v>0.06096438799115934</v>
+        <v>0.03259941675646407</v>
       </c>
       <c r="R5">
-        <v>0.6163275952008346</v>
+        <v>1.279761653213878</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1026,73 +1041,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>1612.4</v>
+        <v>21740.7</v>
       </c>
       <c r="V5">
-        <v>0.1386640981759703</v>
+        <v>0.2340369645930913</v>
       </c>
       <c r="W5">
-        <v>0.07075671918157939</v>
+        <v>0.03712582741973695</v>
       </c>
       <c r="X5">
-        <v>0.1179577415273157</v>
+        <v>0.09250885474156229</v>
       </c>
       <c r="Y5">
-        <v>-0.04720102234573634</v>
+        <v>-0.05538302732182533</v>
       </c>
       <c r="Z5">
-        <v>1.540683974780818</v>
+        <v>1.565260174644321</v>
       </c>
       <c r="AA5">
-        <v>0.0580911541809073</v>
+        <v>0.0421335395936115</v>
       </c>
       <c r="AB5">
-        <v>0.09226217707254612</v>
+        <v>0.08079468208057304</v>
       </c>
       <c r="AC5">
-        <v>-0.03417102289163883</v>
+        <v>-0.03866114248696154</v>
       </c>
       <c r="AD5">
-        <v>5938.3</v>
+        <v>27893.7</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>5938.3</v>
+        <v>27893.7</v>
       </c>
       <c r="AG5">
-        <v>4325.9</v>
+        <v>6153</v>
       </c>
       <c r="AH5">
-        <v>0.3380487749339648</v>
+        <v>0.2309310527535848</v>
       </c>
       <c r="AI5">
-        <v>0.2968437574982005</v>
+        <v>0.3107330723625726</v>
       </c>
       <c r="AJ5">
-        <v>0.2711483013664285</v>
+        <v>0.06212183471937145</v>
       </c>
       <c r="AK5">
-        <v>0.235200408864531</v>
+        <v>0.09044977927784238</v>
       </c>
       <c r="AL5">
-        <v>117.1</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>117.1</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>4.802507076425394</v>
-      </c>
-      <c r="AO5">
-        <v>9.347566182749786</v>
+        <v>8.277062314540059</v>
       </c>
       <c r="AP5">
-        <v>3.498503841488071</v>
-      </c>
-      <c r="AQ5">
-        <v>9.347566182749786</v>
+        <v>1.825816023738872</v>
       </c>
     </row>
     <row r="6">
@@ -1103,7 +1112,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>China Life Insurance Company Limited (SEHK:2628)</t>
+          <t>Hubei Biocause Pharmaceutical Co., Ltd. (SZSE:000627)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1112,46 +1121,43 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.073</v>
-      </c>
-      <c r="E6">
-        <v>0.006860000000000001</v>
+        <v>0.112</v>
       </c>
       <c r="G6">
-        <v>0.1038361972732758</v>
+        <v>0.003939674596701732</v>
       </c>
       <c r="H6">
-        <v>0.1038361972732758</v>
+        <v>0.003939674596701732</v>
       </c>
       <c r="I6">
-        <v>0.05368019204050416</v>
+        <v>-0.008584343594918512</v>
       </c>
       <c r="J6">
-        <v>0.05368019204050416</v>
+        <v>-0.008584343594918512</v>
       </c>
       <c r="K6">
-        <v>4716.1</v>
+        <v>-24.2</v>
       </c>
       <c r="L6">
-        <v>0.04350894608363209</v>
+        <v>-0.003345267552287084</v>
       </c>
       <c r="M6">
-        <v>3607.1</v>
+        <v>185.8</v>
       </c>
       <c r="N6">
-        <v>0.02888950291730238</v>
+        <v>0.09389529007479282</v>
       </c>
       <c r="O6">
-        <v>0.7648480736201522</v>
+        <v>-7.677685950413224</v>
       </c>
       <c r="P6">
-        <v>3607.1</v>
+        <v>185.8</v>
       </c>
       <c r="Q6">
-        <v>0.02888950291730238</v>
+        <v>0.09389529007479282</v>
       </c>
       <c r="R6">
-        <v>0.7648480736201522</v>
+        <v>-7.677685950413224</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1160,73 +1166,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>17037.9</v>
+        <v>3513.2</v>
       </c>
       <c r="V6">
-        <v>0.1364576700825334</v>
+        <v>1.775419446128967</v>
       </c>
       <c r="W6">
-        <v>0.06455052381173984</v>
+        <v>-0.00811155057987531</v>
       </c>
       <c r="X6">
-        <v>0.1030049121360875</v>
+        <v>0.1404396867099254</v>
       </c>
       <c r="Y6">
-        <v>-0.03845438832434762</v>
+        <v>-0.1485512372898007</v>
       </c>
       <c r="Z6">
-        <v>1.062876048228308</v>
+        <v>2.952934933463956</v>
       </c>
       <c r="AA6">
-        <v>0.05705539038414773</v>
+        <v>-0.02534900808229243</v>
       </c>
       <c r="AB6">
-        <v>0.09487461358960687</v>
+        <v>0.07612527641373473</v>
       </c>
       <c r="AC6">
-        <v>-0.03781922320545914</v>
+        <v>-0.1014742844960272</v>
       </c>
       <c r="AD6">
-        <v>20271</v>
+        <v>3479</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>20271</v>
+        <v>3479</v>
       </c>
       <c r="AG6">
-        <v>3233.099999999999</v>
+        <v>-34.19999999999982</v>
       </c>
       <c r="AH6">
-        <v>0.1396752555476316</v>
+        <v>0.6374363296566382</v>
       </c>
       <c r="AI6">
-        <v>0.2378479983385488</v>
+        <v>0.4296122499382564</v>
       </c>
       <c r="AJ6">
-        <v>0.02524053099500669</v>
+        <v>-0.0175871644554149</v>
       </c>
       <c r="AK6">
-        <v>0.04741394481205123</v>
+        <v>-0.007459431163845711</v>
       </c>
       <c r="AL6">
-        <v>2506.6</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>2506.6</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>3.199488612150196</v>
-      </c>
-      <c r="AO6">
-        <v>2.321311737014283</v>
+        <v>-70.56795131845843</v>
       </c>
       <c r="AP6">
-        <v>0.5102987830863202</v>
-      </c>
-      <c r="AQ6">
-        <v>2.321311737014283</v>
+        <v>0.6937119675456352</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hubei Biocause Pharmaceutical Co., Ltd. (SZSE:000627)</t>
+          <t>New China Life Insurance Company Ltd. (SHSE:601336)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1246,46 +1246,49 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0144</v>
+        <v>0.0519</v>
       </c>
       <c r="E7">
-        <v>-0.275</v>
+        <v>0.0007199999999999999</v>
+      </c>
+      <c r="F7">
+        <v>0.174</v>
       </c>
       <c r="G7">
-        <v>0.008541282867191425</v>
+        <v>0.04452878400721479</v>
       </c>
       <c r="H7">
-        <v>0.008541282867191425</v>
+        <v>0.04452878400721479</v>
       </c>
       <c r="I7">
-        <v>0.009685703120638644</v>
+        <v>-0.03767097549977454</v>
       </c>
       <c r="J7">
-        <v>0.009685703120638644</v>
+        <v>-0.03767097549977454</v>
       </c>
       <c r="K7">
-        <v>50</v>
+        <v>1106.3</v>
       </c>
       <c r="L7">
-        <v>0.006978172277117178</v>
+        <v>0.04157147151660905</v>
       </c>
       <c r="M7">
-        <v>91</v>
+        <v>505.7</v>
       </c>
       <c r="N7">
-        <v>0.04020144901926136</v>
+        <v>0.04527264751434634</v>
       </c>
       <c r="O7">
-        <v>1.82</v>
+        <v>0.4571092831962397</v>
       </c>
       <c r="P7">
-        <v>91</v>
+        <v>505.7</v>
       </c>
       <c r="Q7">
-        <v>0.04020144901926136</v>
+        <v>0.04527264751434634</v>
       </c>
       <c r="R7">
-        <v>1.82</v>
+        <v>0.4571092831962397</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1294,67 +1297,70 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>3447.1</v>
+        <v>2327.5</v>
       </c>
       <c r="V7">
-        <v>1.522839724332921</v>
+        <v>0.2083687701990134</v>
       </c>
       <c r="W7">
-        <v>0.01439511717625381</v>
+        <v>0.07866295026948619</v>
       </c>
       <c r="X7">
-        <v>0.1677933004424598</v>
+        <v>0.1217792936685995</v>
       </c>
       <c r="Y7">
-        <v>-0.153398183266206</v>
+        <v>-0.04311634339911333</v>
       </c>
       <c r="Z7">
-        <v>4.775208263912031</v>
+        <v>1.44711441730969</v>
       </c>
       <c r="AA7">
-        <v>0.0462512495834722</v>
+        <v>-0.05451421175984383</v>
       </c>
       <c r="AB7">
-        <v>0.08905128301116036</v>
+        <v>0.07945396487885244</v>
       </c>
       <c r="AC7">
-        <v>-0.04280003342768816</v>
+        <v>-0.1339681766386963</v>
       </c>
       <c r="AD7">
-        <v>3783.9</v>
+        <v>13298.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3783.9</v>
+        <v>13298.7</v>
       </c>
       <c r="AG7">
-        <v>336.8000000000002</v>
+        <v>10971.2</v>
       </c>
       <c r="AH7">
-        <v>0.6256965688300951</v>
+        <v>0.5434962074151573</v>
       </c>
       <c r="AI7">
-        <v>0.4356872272565027</v>
+        <v>0.4724898742272437</v>
       </c>
       <c r="AJ7">
-        <v>0.1295185356099062</v>
+        <v>0.4955083938160812</v>
       </c>
       <c r="AK7">
-        <v>0.0643018061017985</v>
+        <v>0.4249356081879273</v>
       </c>
       <c r="AL7">
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>-973.5</v>
       </c>
       <c r="AN7">
-        <v>44.88612099644129</v>
+        <v>-15.52135854341737</v>
       </c>
       <c r="AP7">
-        <v>3.995255041518389</v>
+        <v>-12.80485527544351</v>
+      </c>
+      <c r="AQ7">
+        <v>1.029789419619928</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/china/china_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ7"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.06455</v>
+        <v>0.0408</v>
       </c>
       <c r="E2">
-        <v>-0.0512</v>
+        <v>0.122</v>
       </c>
       <c r="F2">
-        <v>0.174</v>
+        <v>0.0393</v>
       </c>
       <c r="G2">
-        <v>0.08141788240995586</v>
+        <v>0.04090976553466587</v>
       </c>
       <c r="H2">
-        <v>0.08141788240995586</v>
+        <v>0.04090976553466587</v>
       </c>
       <c r="I2">
-        <v>0.06127046346528753</v>
+        <v>0.1098687366898728</v>
       </c>
       <c r="J2">
-        <v>0.0594903861454784</v>
+        <v>0.09776206078781828</v>
       </c>
       <c r="K2">
-        <v>14922</v>
+        <v>12469.7</v>
       </c>
       <c r="L2">
-        <v>0.04565385796822281</v>
+        <v>0.1076001905268135</v>
       </c>
       <c r="M2">
-        <v>11574.8375</v>
+        <v>2966.4</v>
       </c>
       <c r="N2">
-        <v>0.05598890122355001</v>
+        <v>0.02219414036985745</v>
       </c>
       <c r="O2">
-        <v>0.7756894183085377</v>
+        <v>0.2378886420683737</v>
       </c>
       <c r="P2">
-        <v>10964.8375</v>
+        <v>2966.4</v>
       </c>
       <c r="Q2">
-        <v>0.05303825679797034</v>
+        <v>0.02219414036985745</v>
       </c>
       <c r="R2">
-        <v>0.7348101796005897</v>
+        <v>0.2378886420683737</v>
       </c>
       <c r="S2">
-        <v>610</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.05270052387344531</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>90759.3</v>
+        <v>10903</v>
       </c>
       <c r="V2">
-        <v>0.4390138075647751</v>
+        <v>0.08157453898751206</v>
       </c>
       <c r="W2">
-        <v>0.07866295026948619</v>
+        <v>0.2059085790149836</v>
       </c>
       <c r="X2">
-        <v>0.1217792936685995</v>
+        <v>0.09246762743557496</v>
       </c>
       <c r="Y2">
-        <v>-0.04311634339911333</v>
+        <v>0.1134409515794087</v>
       </c>
       <c r="Z2">
-        <v>0.7310530022753507</v>
+        <v>1.737146317626108</v>
       </c>
       <c r="AA2">
-        <v>0.0421335395936115</v>
+        <v>0.1698270039010983</v>
       </c>
       <c r="AB2">
-        <v>0.07945396487885244</v>
+        <v>0.08520418321913902</v>
       </c>
       <c r="AC2">
-        <v>-0.03866114248696154</v>
+        <v>0.08462282068195924</v>
       </c>
       <c r="AD2">
-        <v>327947.2</v>
+        <v>24367.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>327947.2</v>
+        <v>24367.1</v>
       </c>
       <c r="AG2">
-        <v>237187.9</v>
+        <v>13464.1</v>
       </c>
       <c r="AH2">
-        <v>0.6133503353490498</v>
+        <v>0.1541987293069407</v>
       </c>
       <c r="AI2">
-        <v>0.5583723277880418</v>
+        <v>0.2283423762803032</v>
       </c>
       <c r="AJ2">
-        <v>0.5343003642077985</v>
+        <v>0.09151718653353361</v>
       </c>
       <c r="AK2">
-        <v>0.477654612320815</v>
+        <v>0.1405291723202171</v>
       </c>
       <c r="AL2">
-        <v>3255</v>
+        <v>2889</v>
       </c>
       <c r="AM2">
-        <v>2281.5</v>
+        <v>2889</v>
       </c>
       <c r="AN2">
-        <v>14.35462507824093</v>
+        <v>1.834830538466752</v>
       </c>
       <c r="AO2">
-        <v>6.152473118279571</v>
+        <v>4.407268951194185</v>
       </c>
       <c r="AP2">
-        <v>10.38198642219022</v>
+        <v>1.013840048794078</v>
       </c>
       <c r="AQ2">
-        <v>8.777690116151655</v>
+        <v>4.407268951194185</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sunshine Insurance Group Company Limited (SEHK:6963)</t>
+          <t>China Life Insurance Company Limited (SEHK:2628)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,41 +724,50 @@
           <t>Insurance (Life)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0408</v>
+      </c>
+      <c r="E3">
+        <v>0.122</v>
+      </c>
+      <c r="F3">
+        <v>0.0393</v>
+      </c>
       <c r="G3">
-        <v>0.05997017291945025</v>
+        <v>0.04090976553466587</v>
       </c>
       <c r="H3">
-        <v>0.05997017291945025</v>
+        <v>0.04090976553466587</v>
       </c>
       <c r="I3">
-        <v>0.04946970998985436</v>
+        <v>0.1098687366898728</v>
       </c>
       <c r="J3">
-        <v>0.04228354688694549</v>
+        <v>0.09776206078781828</v>
       </c>
       <c r="K3">
-        <v>705.8</v>
+        <v>12469.7</v>
       </c>
       <c r="L3">
-        <v>0.03913002500374224</v>
+        <v>0.1076001905268135</v>
       </c>
       <c r="M3">
-        <v>287.5375</v>
+        <v>2966.4</v>
       </c>
       <c r="N3">
-        <v>0.04489546575898573</v>
+        <v>0.02219414036985745</v>
       </c>
       <c r="O3">
-        <v>0.4073923207707567</v>
+        <v>0.2378886420683737</v>
       </c>
       <c r="P3">
-        <v>287.5375</v>
+        <v>2966.4</v>
       </c>
       <c r="Q3">
-        <v>0.04489546575898573</v>
+        <v>0.02219414036985745</v>
       </c>
       <c r="R3">
-        <v>0.4073923207707567</v>
+        <v>0.2378886420683737</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,600 +776,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1691.3</v>
+        <v>10903</v>
       </c>
       <c r="V3">
-        <v>0.2640758205040127</v>
+        <v>0.08157453898751206</v>
       </c>
       <c r="W3">
-        <v>0.08675771022580604</v>
+        <v>0.2059085790149836</v>
       </c>
       <c r="X3">
-        <v>0.1114473969901334</v>
+        <v>0.09246762743557496</v>
       </c>
       <c r="Y3">
-        <v>-0.02468968676432735</v>
+        <v>0.1134409515794087</v>
       </c>
       <c r="Z3">
-        <v>1.440886069882251</v>
+        <v>1.737146317626108</v>
       </c>
       <c r="AA3">
-        <v>0.06092577369461279</v>
+        <v>0.1698270039010983</v>
       </c>
       <c r="AB3">
-        <v>0.07990169400143154</v>
+        <v>0.08520418321913902</v>
       </c>
       <c r="AC3">
-        <v>-0.01897592030681875</v>
+        <v>0.08462282068195924</v>
       </c>
       <c r="AD3">
-        <v>5612.4</v>
+        <v>24367.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>5612.4</v>
+        <v>24367.1</v>
       </c>
       <c r="AG3">
-        <v>3921.099999999999</v>
+        <v>13464.1</v>
       </c>
       <c r="AH3">
-        <v>0.4670383623200466</v>
+        <v>0.1541987293069407</v>
       </c>
       <c r="AI3">
-        <v>0.3793571935516577</v>
+        <v>0.2283423762803032</v>
       </c>
       <c r="AJ3">
-        <v>0.3797418092720105</v>
+        <v>0.09151718653353361</v>
       </c>
       <c r="AK3">
-        <v>0.2992475120581232</v>
+        <v>0.1405291723202171</v>
       </c>
       <c r="AL3">
-        <v>22.8</v>
+        <v>2889</v>
       </c>
       <c r="AM3">
-        <v>22.8</v>
+        <v>2889</v>
       </c>
       <c r="AN3">
-        <v>5.386697379786927</v>
+        <v>1.834830538466752</v>
       </c>
       <c r="AO3">
-        <v>39.1359649122807</v>
+        <v>4.407268951194185</v>
       </c>
       <c r="AP3">
-        <v>3.76341299548901</v>
+        <v>1.013840048794078</v>
       </c>
       <c r="AQ3">
-        <v>39.1359649122807</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Ping An Insurance (Group) Company of China, Ltd. (SEHK:2318)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.0341</v>
-      </c>
-      <c r="E4">
-        <v>-0.0512</v>
-      </c>
-      <c r="F4">
-        <v>0.172</v>
-      </c>
-      <c r="G4">
-        <v>0.1190757329349194</v>
-      </c>
-      <c r="H4">
-        <v>0.1190757329349194</v>
-      </c>
-      <c r="I4">
-        <v>0.1021321689677933</v>
-      </c>
-      <c r="J4">
-        <v>0.1021321689677933</v>
-      </c>
-      <c r="K4">
-        <v>10767.8</v>
-      </c>
-      <c r="L4">
-        <v>0.0632873970047249</v>
-      </c>
-      <c r="M4">
-        <v>7567.5</v>
-      </c>
-      <c r="N4">
-        <v>0.08026052454906153</v>
-      </c>
-      <c r="O4">
-        <v>0.7027897992161817</v>
-      </c>
-      <c r="P4">
-        <v>6957.5</v>
-      </c>
-      <c r="Q4">
-        <v>0.07379089521639849</v>
-      </c>
-      <c r="R4">
-        <v>0.6461394156652241</v>
-      </c>
-      <c r="S4">
-        <v>610</v>
-      </c>
-      <c r="T4">
-        <v>0.08060786257020151</v>
-      </c>
-      <c r="U4">
-        <v>61486.6</v>
-      </c>
-      <c r="V4">
-        <v>0.6521237884028183</v>
-      </c>
-      <c r="W4">
-        <v>0.09132746185006005</v>
-      </c>
-      <c r="X4">
-        <v>0.1794569480110285</v>
-      </c>
-      <c r="Y4">
-        <v>-0.08812948616096841</v>
-      </c>
-      <c r="Z4">
-        <v>0.49064907410665</v>
-      </c>
-      <c r="AA4">
-        <v>0.0501110541405517</v>
-      </c>
-      <c r="AB4">
-        <v>0.07826515423242911</v>
-      </c>
-      <c r="AC4">
-        <v>-0.02815410009187741</v>
-      </c>
-      <c r="AD4">
-        <v>277663.4</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>277663.4</v>
-      </c>
-      <c r="AG4">
-        <v>216176.8</v>
-      </c>
-      <c r="AH4">
-        <v>0.7465071255525942</v>
-      </c>
-      <c r="AI4">
-        <v>0.6218369922861445</v>
-      </c>
-      <c r="AJ4">
-        <v>0.6963034301938876</v>
-      </c>
-      <c r="AK4">
-        <v>0.5614477244382713</v>
-      </c>
-      <c r="AL4">
-        <v>3232.2</v>
-      </c>
-      <c r="AM4">
-        <v>3232.2</v>
-      </c>
-      <c r="AN4">
-        <v>14.3567266278186</v>
-      </c>
-      <c r="AO4">
-        <v>5.376183404492297</v>
-      </c>
-      <c r="AP4">
-        <v>11.17753085526078</v>
-      </c>
-      <c r="AQ4">
-        <v>5.376183404492297</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>China Life Insurance Company Limited (SEHK:2628)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D5">
-        <v>0.07719999999999999</v>
-      </c>
-      <c r="E5">
-        <v>-0.0736</v>
-      </c>
-      <c r="F5">
-        <v>0.207</v>
-      </c>
-      <c r="G5">
-        <v>0.03869837759870871</v>
-      </c>
-      <c r="H5">
-        <v>0.03869837759870871</v>
-      </c>
-      <c r="I5">
-        <v>0.02691791452701188</v>
-      </c>
-      <c r="J5">
-        <v>0.02691791452701188</v>
-      </c>
-      <c r="K5">
-        <v>2366.3</v>
-      </c>
-      <c r="L5">
-        <v>0.02257357661880009</v>
-      </c>
-      <c r="M5">
-        <v>3028.3</v>
-      </c>
-      <c r="N5">
-        <v>0.03259941675646407</v>
-      </c>
-      <c r="O5">
-        <v>1.279761653213878</v>
-      </c>
-      <c r="P5">
-        <v>3028.3</v>
-      </c>
-      <c r="Q5">
-        <v>0.03259941675646407</v>
-      </c>
-      <c r="R5">
-        <v>1.279761653213878</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>21740.7</v>
-      </c>
-      <c r="V5">
-        <v>0.2340369645930913</v>
-      </c>
-      <c r="W5">
-        <v>0.03712582741973695</v>
-      </c>
-      <c r="X5">
-        <v>0.09250885474156229</v>
-      </c>
-      <c r="Y5">
-        <v>-0.05538302732182533</v>
-      </c>
-      <c r="Z5">
-        <v>1.565260174644321</v>
-      </c>
-      <c r="AA5">
-        <v>0.0421335395936115</v>
-      </c>
-      <c r="AB5">
-        <v>0.08079468208057304</v>
-      </c>
-      <c r="AC5">
-        <v>-0.03866114248696154</v>
-      </c>
-      <c r="AD5">
-        <v>27893.7</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>27893.7</v>
-      </c>
-      <c r="AG5">
-        <v>6153</v>
-      </c>
-      <c r="AH5">
-        <v>0.2309310527535848</v>
-      </c>
-      <c r="AI5">
-        <v>0.3107330723625726</v>
-      </c>
-      <c r="AJ5">
-        <v>0.06212183471937145</v>
-      </c>
-      <c r="AK5">
-        <v>0.09044977927784238</v>
-      </c>
-      <c r="AL5">
-        <v>0</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>8.277062314540059</v>
-      </c>
-      <c r="AP5">
-        <v>1.825816023738872</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Hubei Biocause Pharmaceutical Co., Ltd. (SZSE:000627)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>0.112</v>
-      </c>
-      <c r="G6">
-        <v>0.003939674596701732</v>
-      </c>
-      <c r="H6">
-        <v>0.003939674596701732</v>
-      </c>
-      <c r="I6">
-        <v>-0.008584343594918512</v>
-      </c>
-      <c r="J6">
-        <v>-0.008584343594918512</v>
-      </c>
-      <c r="K6">
-        <v>-24.2</v>
-      </c>
-      <c r="L6">
-        <v>-0.003345267552287084</v>
-      </c>
-      <c r="M6">
-        <v>185.8</v>
-      </c>
-      <c r="N6">
-        <v>0.09389529007479282</v>
-      </c>
-      <c r="O6">
-        <v>-7.677685950413224</v>
-      </c>
-      <c r="P6">
-        <v>185.8</v>
-      </c>
-      <c r="Q6">
-        <v>0.09389529007479282</v>
-      </c>
-      <c r="R6">
-        <v>-7.677685950413224</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>3513.2</v>
-      </c>
-      <c r="V6">
-        <v>1.775419446128967</v>
-      </c>
-      <c r="W6">
-        <v>-0.00811155057987531</v>
-      </c>
-      <c r="X6">
-        <v>0.1404396867099254</v>
-      </c>
-      <c r="Y6">
-        <v>-0.1485512372898007</v>
-      </c>
-      <c r="Z6">
-        <v>2.952934933463956</v>
-      </c>
-      <c r="AA6">
-        <v>-0.02534900808229243</v>
-      </c>
-      <c r="AB6">
-        <v>0.07612527641373473</v>
-      </c>
-      <c r="AC6">
-        <v>-0.1014742844960272</v>
-      </c>
-      <c r="AD6">
-        <v>3479</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>3479</v>
-      </c>
-      <c r="AG6">
-        <v>-34.19999999999982</v>
-      </c>
-      <c r="AH6">
-        <v>0.6374363296566382</v>
-      </c>
-      <c r="AI6">
-        <v>0.4296122499382564</v>
-      </c>
-      <c r="AJ6">
-        <v>-0.0175871644554149</v>
-      </c>
-      <c r="AK6">
-        <v>-0.007459431163845711</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>-70.56795131845843</v>
-      </c>
-      <c r="AP6">
-        <v>0.6937119675456352</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>New China Life Insurance Company Ltd. (SHSE:601336)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Insurance (Life)</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>0.0519</v>
-      </c>
-      <c r="E7">
-        <v>0.0007199999999999999</v>
-      </c>
-      <c r="F7">
-        <v>0.174</v>
-      </c>
-      <c r="G7">
-        <v>0.04452878400721479</v>
-      </c>
-      <c r="H7">
-        <v>0.04452878400721479</v>
-      </c>
-      <c r="I7">
-        <v>-0.03767097549977454</v>
-      </c>
-      <c r="J7">
-        <v>-0.03767097549977454</v>
-      </c>
-      <c r="K7">
-        <v>1106.3</v>
-      </c>
-      <c r="L7">
-        <v>0.04157147151660905</v>
-      </c>
-      <c r="M7">
-        <v>505.7</v>
-      </c>
-      <c r="N7">
-        <v>0.04527264751434634</v>
-      </c>
-      <c r="O7">
-        <v>0.4571092831962397</v>
-      </c>
-      <c r="P7">
-        <v>505.7</v>
-      </c>
-      <c r="Q7">
-        <v>0.04527264751434634</v>
-      </c>
-      <c r="R7">
-        <v>0.4571092831962397</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>2327.5</v>
-      </c>
-      <c r="V7">
-        <v>0.2083687701990134</v>
-      </c>
-      <c r="W7">
-        <v>0.07866295026948619</v>
-      </c>
-      <c r="X7">
-        <v>0.1217792936685995</v>
-      </c>
-      <c r="Y7">
-        <v>-0.04311634339911333</v>
-      </c>
-      <c r="Z7">
-        <v>1.44711441730969</v>
-      </c>
-      <c r="AA7">
-        <v>-0.05451421175984383</v>
-      </c>
-      <c r="AB7">
-        <v>0.07945396487885244</v>
-      </c>
-      <c r="AC7">
-        <v>-0.1339681766386963</v>
-      </c>
-      <c r="AD7">
-        <v>13298.7</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>13298.7</v>
-      </c>
-      <c r="AG7">
-        <v>10971.2</v>
-      </c>
-      <c r="AH7">
-        <v>0.5434962074151573</v>
-      </c>
-      <c r="AI7">
-        <v>0.4724898742272437</v>
-      </c>
-      <c r="AJ7">
-        <v>0.4955083938160812</v>
-      </c>
-      <c r="AK7">
-        <v>0.4249356081879273</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>-973.5</v>
-      </c>
-      <c r="AN7">
-        <v>-15.52135854341737</v>
-      </c>
-      <c r="AP7">
-        <v>-12.80485527544351</v>
-      </c>
-      <c r="AQ7">
-        <v>1.029789419619928</v>
+        <v>4.407268951194185</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/china/china_insurance_life.xlsx
+++ b/research/traditional_assets/database/data/china/china_insurance_life.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0408</v>
+        <v>-0.04355000000000001</v>
       </c>
       <c r="E2">
-        <v>0.122</v>
+        <v>0.08460000000000001</v>
       </c>
       <c r="F2">
-        <v>0.0393</v>
+        <v>0.0983</v>
       </c>
       <c r="G2">
-        <v>0.04090976553466587</v>
+        <v>0.106448655764862</v>
       </c>
       <c r="H2">
-        <v>0.04090976553466587</v>
+        <v>0.106448655764862</v>
       </c>
       <c r="I2">
-        <v>0.1098687366898728</v>
+        <v>0.1578873584309624</v>
       </c>
       <c r="J2">
-        <v>0.09776206078781828</v>
+        <v>0.1485674064511066</v>
       </c>
       <c r="K2">
-        <v>12469.7</v>
+        <v>31908.1</v>
       </c>
       <c r="L2">
-        <v>0.1076001905268135</v>
+        <v>0.1205711733471583</v>
       </c>
       <c r="M2">
-        <v>2966.4</v>
+        <v>13897.4</v>
       </c>
       <c r="N2">
-        <v>0.02219414036985745</v>
+        <v>0.05049813557979434</v>
       </c>
       <c r="O2">
-        <v>0.2378886420683737</v>
+        <v>0.4355445795895086</v>
       </c>
       <c r="P2">
-        <v>2966.4</v>
+        <v>11316.6</v>
       </c>
       <c r="Q2">
-        <v>0.02219414036985745</v>
+        <v>0.04112043987381098</v>
       </c>
       <c r="R2">
-        <v>0.2378886420683737</v>
+        <v>0.3546622957806952</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>2580.799999999999</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.1857038007109243</v>
       </c>
       <c r="U2">
-        <v>10903</v>
+        <v>85492.59999999999</v>
       </c>
       <c r="V2">
-        <v>0.08157453898751206</v>
+        <v>0.3106492513613428</v>
       </c>
       <c r="W2">
-        <v>0.2059085790149836</v>
+        <v>0.162858419018577</v>
       </c>
       <c r="X2">
-        <v>0.09246762743557496</v>
+        <v>0.1274279055868816</v>
       </c>
       <c r="Y2">
-        <v>0.1134409515794087</v>
+        <v>0.03543051343169537</v>
       </c>
       <c r="Z2">
-        <v>1.737146317626108</v>
+        <v>0.6091846414530497</v>
       </c>
       <c r="AA2">
-        <v>0.1698270039010983</v>
+        <v>0.1024052761473609</v>
       </c>
       <c r="AB2">
-        <v>0.08520418321913902</v>
+        <v>0.08215439728329836</v>
       </c>
       <c r="AC2">
-        <v>0.08462282068195924</v>
+        <v>0.02286936912956077</v>
       </c>
       <c r="AD2">
-        <v>24367.1</v>
+        <v>359973.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>24367.1</v>
+        <v>359973.7</v>
       </c>
       <c r="AG2">
-        <v>13464.1</v>
+        <v>274481.1</v>
       </c>
       <c r="AH2">
-        <v>0.1541987293069407</v>
+        <v>0.5667271587151923</v>
       </c>
       <c r="AI2">
-        <v>0.2283423762803032</v>
+        <v>0.5599600843734833</v>
       </c>
       <c r="AJ2">
-        <v>0.09151718653353361</v>
+        <v>0.499340443193794</v>
       </c>
       <c r="AK2">
-        <v>0.1405291723202171</v>
+        <v>0.4924634448548291</v>
       </c>
       <c r="AL2">
-        <v>2889</v>
+        <v>6229.6</v>
       </c>
       <c r="AM2">
-        <v>2889</v>
+        <v>6229.6</v>
       </c>
       <c r="AN2">
-        <v>1.834830538466752</v>
+        <v>8.073965167266651</v>
       </c>
       <c r="AO2">
-        <v>4.407268951194185</v>
+        <v>6.707252472068832</v>
       </c>
       <c r="AP2">
-        <v>1.013840048794078</v>
+        <v>6.156424317868319</v>
       </c>
       <c r="AQ2">
-        <v>4.407268951194185</v>
+        <v>6.707252472068832</v>
       </c>
     </row>
     <row r="3">
@@ -785,10 +785,10 @@
         <v>0.2059085790149836</v>
       </c>
       <c r="X3">
-        <v>0.09246762743557496</v>
+        <v>0.09244702331473677</v>
       </c>
       <c r="Y3">
-        <v>0.1134409515794087</v>
+        <v>0.1134615557002469</v>
       </c>
       <c r="Z3">
         <v>1.737146317626108</v>
@@ -797,10 +797,10 @@
         <v>0.1698270039010983</v>
       </c>
       <c r="AB3">
-        <v>0.08520418321913902</v>
+        <v>0.08518675622755256</v>
       </c>
       <c r="AC3">
-        <v>0.08462282068195924</v>
+        <v>0.08464024767354569</v>
       </c>
       <c r="AD3">
         <v>24367.1</v>
@@ -843,6 +843,405 @@
       </c>
       <c r="AQ3">
         <v>4.407268951194185</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>New China Life Insurance Company Ltd. (SHSE:601336)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>-0.175</v>
+      </c>
+      <c r="E4">
+        <v>0.08460000000000001</v>
+      </c>
+      <c r="F4">
+        <v>0.345</v>
+      </c>
+      <c r="G4">
+        <v>0.1531217735622142</v>
+      </c>
+      <c r="H4">
+        <v>0.1531217735622142</v>
+      </c>
+      <c r="I4">
+        <v>0.408264219017688</v>
+      </c>
+      <c r="J4">
+        <v>0.4030667567756506</v>
+      </c>
+      <c r="K4">
+        <v>2829.9</v>
+      </c>
+      <c r="L4">
+        <v>0.3210723970092695</v>
+      </c>
+      <c r="M4">
+        <v>2570.4</v>
+      </c>
+      <c r="N4">
+        <v>0.148219907968031</v>
+      </c>
+      <c r="O4">
+        <v>0.9083006466659599</v>
+      </c>
+      <c r="P4">
+        <v>514.9</v>
+      </c>
+      <c r="Q4">
+        <v>0.02969126618920758</v>
+      </c>
+      <c r="R4">
+        <v>0.18194989222234</v>
+      </c>
+      <c r="S4">
+        <v>2055.5</v>
+      </c>
+      <c r="T4">
+        <v>0.7996809835045129</v>
+      </c>
+      <c r="U4">
+        <v>3342.6</v>
+      </c>
+      <c r="V4">
+        <v>0.1927481576306958</v>
+      </c>
+      <c r="W4">
+        <v>0.1906401153312405</v>
+      </c>
+      <c r="X4">
+        <v>0.1436522729216752</v>
+      </c>
+      <c r="Y4">
+        <v>0.04698784240956527</v>
+      </c>
+      <c r="Z4">
+        <v>0.3414202375326355</v>
+      </c>
+      <c r="AA4">
+        <v>0.1376151478398516</v>
+      </c>
+      <c r="AB4">
+        <v>0.08077399391277015</v>
+      </c>
+      <c r="AC4">
+        <v>0.05684115392708147</v>
+      </c>
+      <c r="AD4">
+        <v>32014</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>32014</v>
+      </c>
+      <c r="AG4">
+        <v>28671.4</v>
+      </c>
+      <c r="AH4">
+        <v>0.648637039618444</v>
+      </c>
+      <c r="AI4">
+        <v>0.7114743970113364</v>
+      </c>
+      <c r="AJ4">
+        <v>0.6231124981527041</v>
+      </c>
+      <c r="AK4">
+        <v>0.6883211976732182</v>
+      </c>
+      <c r="AL4">
+        <v>405</v>
+      </c>
+      <c r="AM4">
+        <v>405</v>
+      </c>
+      <c r="AN4">
+        <v>8.50734766548856</v>
+      </c>
+      <c r="AO4">
+        <v>8.884938271604938</v>
+      </c>
+      <c r="AP4">
+        <v>7.619090643352556</v>
+      </c>
+      <c r="AQ4">
+        <v>8.884938271604938</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Ping An Insurance (Group) Company of China, Ltd. (SHSE:601318)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.0541</v>
+      </c>
+      <c r="E5">
+        <v>-0.0574</v>
+      </c>
+      <c r="F5">
+        <v>0.0983</v>
+      </c>
+      <c r="G5">
+        <v>0.166479419037828</v>
+      </c>
+      <c r="H5">
+        <v>0.166479419037828</v>
+      </c>
+      <c r="I5">
+        <v>0.1920333154162079</v>
+      </c>
+      <c r="J5">
+        <v>0.1702963601692658</v>
+      </c>
+      <c r="K5">
+        <v>16718.5</v>
+      </c>
+      <c r="L5">
+        <v>0.1246383337520623</v>
+      </c>
+      <c r="M5">
+        <v>8253.699999999999</v>
+      </c>
+      <c r="N5">
+        <v>0.06818619290933649</v>
+      </c>
+      <c r="O5">
+        <v>0.4936866345664981</v>
+      </c>
+      <c r="P5">
+        <v>7728.4</v>
+      </c>
+      <c r="Q5">
+        <v>0.0638465383137885</v>
+      </c>
+      <c r="R5">
+        <v>0.4622663516463797</v>
+      </c>
+      <c r="S5">
+        <v>525.2999999999993</v>
+      </c>
+      <c r="T5">
+        <v>0.06364418382058948</v>
+      </c>
+      <c r="U5">
+        <v>70059.2</v>
+      </c>
+      <c r="V5">
+        <v>0.5787792294696666</v>
+      </c>
+      <c r="W5">
+        <v>0.1350767227059135</v>
+      </c>
+      <c r="X5">
+        <v>0.1633905221802576</v>
+      </c>
+      <c r="Y5">
+        <v>-0.02831379947434404</v>
+      </c>
+      <c r="Z5">
+        <v>0.3945792170078176</v>
+      </c>
+      <c r="AA5">
+        <v>0.0671954044548702</v>
+      </c>
+      <c r="AB5">
+        <v>0.07829782012283013</v>
+      </c>
+      <c r="AC5">
+        <v>-0.01110241566795993</v>
+      </c>
+      <c r="AD5">
+        <v>301089.9</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>301089.9</v>
+      </c>
+      <c r="AG5">
+        <v>231030.7</v>
+      </c>
+      <c r="AH5">
+        <v>0.7132526358778821</v>
+      </c>
+      <c r="AI5">
+        <v>0.6227161053519602</v>
+      </c>
+      <c r="AJ5">
+        <v>0.656193300787441</v>
+      </c>
+      <c r="AK5">
+        <v>0.5587854923733497</v>
+      </c>
+      <c r="AL5">
+        <v>2935.6</v>
+      </c>
+      <c r="AM5">
+        <v>2935.6</v>
+      </c>
+      <c r="AN5">
+        <v>10.81827491053335</v>
+      </c>
+      <c r="AO5">
+        <v>8.774560566834719</v>
+      </c>
+      <c r="AP5">
+        <v>8.301021141436355</v>
+      </c>
+      <c r="AQ5">
+        <v>8.774560566834719</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hubei Biocause Pharmaceutical Co., Ltd. (SZSE:000627)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Life)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>-0.033</v>
+      </c>
+      <c r="G6">
+        <v>-0.04322647362978284</v>
+      </c>
+      <c r="H6">
+        <v>-0.04322647362978284</v>
+      </c>
+      <c r="I6">
+        <v>-0.05275766976904516</v>
+      </c>
+      <c r="J6">
+        <v>-0.05275766976904516</v>
+      </c>
+      <c r="K6">
+        <v>-110</v>
+      </c>
+      <c r="L6">
+        <v>-0.01895897966218545</v>
+      </c>
+      <c r="M6">
+        <v>106.9</v>
+      </c>
+      <c r="N6">
+        <v>0.03381841189496994</v>
+      </c>
+      <c r="O6">
+        <v>-0.9718181818181819</v>
+      </c>
+      <c r="P6">
+        <v>106.9</v>
+      </c>
+      <c r="Q6">
+        <v>0.03381841189496994</v>
+      </c>
+      <c r="R6">
+        <v>-0.9718181818181819</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>1187.8</v>
+      </c>
+      <c r="V6">
+        <v>0.3757671622904144</v>
+      </c>
+      <c r="W6">
+        <v>-0.03891738899699275</v>
+      </c>
+      <c r="X6">
+        <v>0.1112035382520881</v>
+      </c>
+      <c r="Y6">
+        <v>-0.1501209272490808</v>
+      </c>
+      <c r="Z6">
+        <v>2.985028553789165</v>
+      </c>
+      <c r="AA6">
+        <v>-0.1574831506919792</v>
+      </c>
+      <c r="AB6">
+        <v>0.08353480065382657</v>
+      </c>
+      <c r="AC6">
+        <v>-0.2410179513458058</v>
+      </c>
+      <c r="AD6">
+        <v>2502.7</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>2502.7</v>
+      </c>
+      <c r="AG6">
+        <v>1314.9</v>
+      </c>
+      <c r="AH6">
+        <v>0.441884280593958</v>
+      </c>
+      <c r="AI6">
+        <v>0.3277673005395778</v>
+      </c>
+      <c r="AJ6">
+        <v>0.2937733193324247</v>
+      </c>
+      <c r="AK6">
+        <v>0.2039300226433823</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>-8.615146299483648</v>
+      </c>
+      <c r="AP6">
+        <v>-4.526333907056798</v>
       </c>
     </row>
   </sheetData>
